--- a/output/roomself_excel/6395.xlsx
+++ b/output/roomself_excel/6395.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>650519</v>
+        <v>197696</v>
       </c>
       <c r="D2" t="n">
-        <v>9456</v>
+        <v>4020</v>
       </c>
       <c r="E2" t="n">
-        <v>1214</v>
+        <v>537</v>
       </c>
       <c r="F2" t="n">
-        <v>974</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>197696</v>
+        <v>42294</v>
       </c>
       <c r="D3" t="n">
-        <v>4020</v>
+        <v>1700</v>
       </c>
       <c r="E3" t="n">
-        <v>851</v>
+        <v>159</v>
       </c>
       <c r="F3" t="n">
-        <v>537</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>151424</v>
+        <v>15416</v>
       </c>
       <c r="D4" t="n">
-        <v>3120</v>
+        <v>1032</v>
       </c>
       <c r="E4" t="n">
-        <v>439</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>387</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2537</v>
+        <v>43890</v>
       </c>
       <c r="D5" t="n">
-        <v>408</v>
+        <v>1724</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="F5" t="n">
         <v>23</v>
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>211556</v>
+        <v>650519</v>
       </c>
       <c r="D6" t="n">
-        <v>3720</v>
+        <v>9456</v>
       </c>
       <c r="E6" t="n">
-        <v>934</v>
+        <v>1096</v>
       </c>
       <c r="F6" t="n">
-        <v>678</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>42294</v>
+        <v>151424</v>
       </c>
       <c r="D7" t="n">
-        <v>1700</v>
+        <v>3120</v>
       </c>
       <c r="E7" t="n">
-        <v>159</v>
+        <v>439</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8">
@@ -598,17 +598,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>43890</v>
+        <v>2537</v>
       </c>
       <c r="D8" t="n">
-        <v>1724</v>
+        <v>408</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15416</v>
+        <v>211556</v>
       </c>
       <c r="D9" t="n">
-        <v>1032</v>
+        <v>3720</v>
       </c>
       <c r="E9" t="n">
-        <v>94</v>
+        <v>678</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10">

--- a/output/roomself_excel/6395.xlsx
+++ b/output/roomself_excel/6395.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>4020</v>
       </c>
-      <c r="E2" t="n">
-        <v>537</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>441</v>
+        <v>396</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>109</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +533,20 @@
       <c r="D3" t="n">
         <v>1700</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>159</v>
       </c>
-      <c r="F3" t="n">
-        <v>23</v>
-      </c>
+      <c r="G3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +563,20 @@
       <c r="D4" t="n">
         <v>1032</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>94</v>
       </c>
-      <c r="F4" t="n">
-        <v>23</v>
-      </c>
+      <c r="G4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +593,20 @@
       <c r="D5" t="n">
         <v>1724</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>81</v>
       </c>
-      <c r="F5" t="n">
-        <v>23</v>
-      </c>
+      <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +623,27 @@
       <c r="D6" t="n">
         <v>9456</v>
       </c>
-      <c r="E6" t="n">
-        <v>1096</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>974</v>
+        <v>1755</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>882</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -585,11 +661,27 @@
       <c r="D7" t="n">
         <v>3120</v>
       </c>
-      <c r="E7" t="n">
-        <v>439</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>387</v>
+        <v>364</v>
+      </c>
+      <c r="G7" t="n">
+        <v>23</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>416</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>408</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>59</v>
       </c>
-      <c r="F8" t="n">
-        <v>23</v>
-      </c>
+      <c r="G8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,20 @@
       <c r="D9" t="n">
         <v>3720</v>
       </c>
-      <c r="E9" t="n">
-        <v>678</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>425</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="G9" t="n">
+        <v>23</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +759,27 @@
       <c r="D10" t="n">
         <v>2736</v>
       </c>
-      <c r="E10" t="n">
-        <v>588</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>142</v>
+        <v>284</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>542</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
